--- a/artfynd/A 49671-2022 artfynd.xlsx
+++ b/artfynd/A 49671-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124878415</v>
+        <v>124879281</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>56856</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100065</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478649</v>
+        <v>478829</v>
       </c>
       <c r="R2" t="n">
-        <v>6847660</v>
+        <v>6847313</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124879281</v>
+        <v>124879880</v>
       </c>
       <c r="B3" t="n">
-        <v>56856</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100065</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478829</v>
+        <v>478836</v>
       </c>
       <c r="R3" t="n">
-        <v>6847313</v>
+        <v>6847547</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124879781</v>
+        <v>124879020</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1025,7 +1025,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1039,13 +1039,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478839</v>
+        <v>478692</v>
       </c>
       <c r="R5" t="n">
-        <v>6847520</v>
+        <v>6847427</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124878885</v>
+        <v>124880942</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1236,29 +1236,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478709</v>
+        <v>478640</v>
       </c>
       <c r="R7" t="n">
-        <v>6847442</v>
+        <v>6847434</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,7 +1305,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124878086</v>
+        <v>124880882</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1347,17 +1338,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478613</v>
+        <v>478627</v>
       </c>
       <c r="R8" t="n">
-        <v>6847629</v>
+        <v>6847481</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1416,7 +1416,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124877547</v>
+        <v>124878260</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1465,13 +1465,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478641</v>
+        <v>478636</v>
       </c>
       <c r="R9" t="n">
-        <v>6847702</v>
+        <v>6847633</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124880539</v>
+        <v>124880175</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1560,20 +1560,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bäverbäcken, Bäverbäcken, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478707</v>
+        <v>478795</v>
       </c>
       <c r="R10" t="n">
-        <v>6847701</v>
+        <v>6847652</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1629,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124880882</v>
+        <v>124877845</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1664,7 +1673,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1674,17 +1683,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478627</v>
+        <v>478609</v>
       </c>
       <c r="R11" t="n">
-        <v>6847481</v>
+        <v>6847684</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1740,7 +1749,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124880144</v>
+        <v>124880961</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1773,26 +1782,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478793</v>
+        <v>478643</v>
       </c>
       <c r="R12" t="n">
-        <v>6847622</v>
+        <v>6847426</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1851,10 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124878967</v>
+        <v>124880228</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,25 +1863,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1891,13 +1891,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478709</v>
+        <v>478766</v>
       </c>
       <c r="R13" t="n">
-        <v>6847428</v>
+        <v>6847674</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124877845</v>
+        <v>124877633</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -1986,29 +1986,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478609</v>
+        <v>478616</v>
       </c>
       <c r="R14" t="n">
-        <v>6847684</v>
+        <v>6847709</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2064,7 +2055,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124880175</v>
+        <v>124879945</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2097,29 +2088,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478795</v>
+        <v>478826</v>
       </c>
       <c r="R15" t="n">
-        <v>6847652</v>
+        <v>6847564</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2175,7 +2157,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124877917</v>
+        <v>124880144</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2208,17 +2190,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478615</v>
+        <v>478793</v>
       </c>
       <c r="R16" t="n">
-        <v>6847687</v>
+        <v>6847622</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2277,7 +2268,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124877633</v>
+        <v>124879781</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2310,17 +2301,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478616</v>
+        <v>478839</v>
       </c>
       <c r="R17" t="n">
-        <v>6847709</v>
+        <v>6847520</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2379,10 +2379,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124880961</v>
+        <v>124878967</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2391,25 +2391,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2419,13 +2419,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478643</v>
+        <v>478709</v>
       </c>
       <c r="R18" t="n">
-        <v>6847426</v>
+        <v>6847428</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124880417</v>
+        <v>124878229</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2514,20 +2514,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478732</v>
+        <v>478635</v>
       </c>
       <c r="R19" t="n">
-        <v>6847699</v>
+        <v>6847637</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2583,7 +2592,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124880942</v>
+        <v>124878086</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2619,14 +2628,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478640</v>
+        <v>478613</v>
       </c>
       <c r="R20" t="n">
-        <v>6847434</v>
+        <v>6847629</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2685,7 +2694,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124878260</v>
+        <v>124877779</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -2720,7 +2729,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2734,13 +2743,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478636</v>
+        <v>478611</v>
       </c>
       <c r="R21" t="n">
-        <v>6847633</v>
+        <v>6847683</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2796,7 +2805,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124880228</v>
+        <v>124880417</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -2836,13 +2845,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478766</v>
+        <v>478732</v>
       </c>
       <c r="R22" t="n">
-        <v>6847674</v>
+        <v>6847699</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2898,7 +2907,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124878229</v>
+        <v>124878885</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -2933,7 +2942,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2943,14 +2952,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478635</v>
+        <v>478709</v>
       </c>
       <c r="R23" t="n">
-        <v>6847637</v>
+        <v>6847442</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3009,7 +3018,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124879945</v>
+        <v>124880539</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3045,17 +3054,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Bäverbäcken, Bäverbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478826</v>
+        <v>478707</v>
       </c>
       <c r="R24" t="n">
-        <v>6847564</v>
+        <v>6847701</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3111,7 +3120,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124877779</v>
+        <v>124877547</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3160,13 +3169,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478611</v>
+        <v>478641</v>
       </c>
       <c r="R25" t="n">
-        <v>6847683</v>
+        <v>6847702</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3222,7 +3231,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124879020</v>
+        <v>124878415</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3255,29 +3264,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478692</v>
+        <v>478649</v>
       </c>
       <c r="R26" t="n">
-        <v>6847427</v>
+        <v>6847660</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124879880</v>
+        <v>124877917</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3369,14 +3369,14 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478836</v>
+        <v>478615</v>
       </c>
       <c r="R27" t="n">
-        <v>6847547</v>
+        <v>6847687</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 49671-2022 artfynd.xlsx
+++ b/artfynd/A 49671-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124879281</v>
+        <v>124877845</v>
       </c>
       <c r="B2" t="n">
-        <v>56856</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100065</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478829</v>
+        <v>478609</v>
       </c>
       <c r="R2" t="n">
-        <v>6847313</v>
+        <v>6847684</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -879,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124878842</v>
+        <v>124877779</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -914,7 +923,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -924,17 +933,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478703</v>
+        <v>478611</v>
       </c>
       <c r="R4" t="n">
-        <v>6847444</v>
+        <v>6847683</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,7 +999,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124879020</v>
+        <v>124880175</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1025,7 +1034,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1039,13 +1048,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478692</v>
+        <v>478795</v>
       </c>
       <c r="R5" t="n">
-        <v>6847427</v>
+        <v>6847652</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,7 +1110,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124880456</v>
+        <v>124880539</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1137,17 +1146,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Bäverbäcken, Bäverbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478725</v>
+        <v>478707</v>
       </c>
       <c r="R6" t="n">
-        <v>6847685</v>
+        <v>6847701</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,7 +1212,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124880942</v>
+        <v>124878842</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1236,17 +1245,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478640</v>
+        <v>478703</v>
       </c>
       <c r="R7" t="n">
-        <v>6847434</v>
+        <v>6847444</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1305,7 +1323,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124880882</v>
+        <v>124879781</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1340,7 +1358,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1354,13 +1372,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478627</v>
+        <v>478839</v>
       </c>
       <c r="R8" t="n">
-        <v>6847481</v>
+        <v>6847520</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1416,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124878260</v>
+        <v>124879281</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>56856</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1428,47 +1446,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100065</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478636</v>
+        <v>478829</v>
       </c>
       <c r="R9" t="n">
-        <v>6847633</v>
+        <v>6847313</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1527,7 +1536,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124880175</v>
+        <v>124880942</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1560,29 +1569,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478795</v>
+        <v>478640</v>
       </c>
       <c r="R10" t="n">
-        <v>6847652</v>
+        <v>6847434</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124877845</v>
+        <v>124878229</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1687,13 +1687,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478609</v>
+        <v>478635</v>
       </c>
       <c r="R11" t="n">
-        <v>6847684</v>
+        <v>6847637</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124880961</v>
+        <v>124880417</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478643</v>
+        <v>478732</v>
       </c>
       <c r="R12" t="n">
-        <v>6847426</v>
+        <v>6847699</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124880228</v>
+        <v>124877547</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1884,20 +1884,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478766</v>
+        <v>478641</v>
       </c>
       <c r="R13" t="n">
-        <v>6847674</v>
+        <v>6847702</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1953,7 +1962,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124877633</v>
+        <v>124880882</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -1986,20 +1995,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478616</v>
+        <v>478627</v>
       </c>
       <c r="R14" t="n">
-        <v>6847709</v>
+        <v>6847481</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2055,7 +2073,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124879945</v>
+        <v>124880228</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2095,10 +2113,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478826</v>
+        <v>478766</v>
       </c>
       <c r="R15" t="n">
-        <v>6847564</v>
+        <v>6847674</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2157,7 +2175,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124880144</v>
+        <v>124878885</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2192,7 +2210,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2206,10 +2224,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478793</v>
+        <v>478709</v>
       </c>
       <c r="R16" t="n">
-        <v>6847622</v>
+        <v>6847442</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2268,7 +2286,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124879781</v>
+        <v>124877633</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2301,26 +2319,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478839</v>
+        <v>478616</v>
       </c>
       <c r="R17" t="n">
-        <v>6847520</v>
+        <v>6847709</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2379,10 +2388,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124878967</v>
+        <v>124877917</v>
       </c>
       <c r="B18" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2391,41 +2400,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478709</v>
+        <v>478615</v>
       </c>
       <c r="R18" t="n">
-        <v>6847428</v>
+        <v>6847687</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2481,7 +2490,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124878229</v>
+        <v>124878086</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2514,29 +2523,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478635</v>
+        <v>478613</v>
       </c>
       <c r="R19" t="n">
-        <v>6847637</v>
+        <v>6847629</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124878086</v>
+        <v>124879945</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2628,17 +2628,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478613</v>
+        <v>478826</v>
       </c>
       <c r="R20" t="n">
-        <v>6847629</v>
+        <v>6847564</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2694,10 +2694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124877779</v>
+        <v>124878967</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2706,50 +2706,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478611</v>
+        <v>478709</v>
       </c>
       <c r="R21" t="n">
-        <v>6847683</v>
+        <v>6847428</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2805,7 +2796,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124880417</v>
+        <v>124880961</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -2845,13 +2836,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478732</v>
+        <v>478643</v>
       </c>
       <c r="R22" t="n">
-        <v>6847699</v>
+        <v>6847426</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2907,7 +2898,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124878885</v>
+        <v>124879020</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -2942,7 +2933,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2956,13 +2947,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478709</v>
+        <v>478692</v>
       </c>
       <c r="R23" t="n">
-        <v>6847442</v>
+        <v>6847427</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3018,7 +3009,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124880539</v>
+        <v>124880456</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3054,17 +3045,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bäverbäcken, Bäverbäcken, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478707</v>
+        <v>478725</v>
       </c>
       <c r="R24" t="n">
-        <v>6847701</v>
+        <v>6847685</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3120,7 +3111,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124877547</v>
+        <v>124878415</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3153,29 +3144,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478641</v>
+        <v>478649</v>
       </c>
       <c r="R25" t="n">
-        <v>6847702</v>
+        <v>6847660</v>
       </c>
       <c r="S25" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3231,7 +3213,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124878415</v>
+        <v>124878260</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3264,20 +3246,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478649</v>
+        <v>478636</v>
       </c>
       <c r="R26" t="n">
-        <v>6847660</v>
+        <v>6847633</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3333,7 +3324,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124877917</v>
+        <v>124880144</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3366,17 +3357,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478615</v>
+        <v>478793</v>
       </c>
       <c r="R27" t="n">
-        <v>6847687</v>
+        <v>6847622</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 49671-2022 artfynd.xlsx
+++ b/artfynd/A 49671-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124877845</v>
+        <v>124880961</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -708,29 +708,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478609</v>
+        <v>478643</v>
       </c>
       <c r="R2" t="n">
-        <v>6847684</v>
+        <v>6847426</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124879880</v>
+        <v>124878086</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -822,17 +813,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478836</v>
+        <v>478613</v>
       </c>
       <c r="R3" t="n">
-        <v>6847547</v>
+        <v>6847629</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124877779</v>
+        <v>124880456</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -921,26 +912,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478611</v>
+        <v>478725</v>
       </c>
       <c r="R4" t="n">
-        <v>6847683</v>
+        <v>6847685</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124880175</v>
+        <v>124880942</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1032,29 +1014,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478795</v>
+        <v>478640</v>
       </c>
       <c r="R5" t="n">
-        <v>6847652</v>
+        <v>6847434</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124880539</v>
+        <v>124878415</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1146,17 +1119,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bäverbäcken, Bäverbäcken, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478707</v>
+        <v>478649</v>
       </c>
       <c r="R6" t="n">
-        <v>6847701</v>
+        <v>6847660</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124878842</v>
+        <v>124878260</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1247,7 +1220,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1257,14 +1230,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478703</v>
+        <v>478636</v>
       </c>
       <c r="R7" t="n">
-        <v>6847444</v>
+        <v>6847633</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1323,7 +1296,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124879781</v>
+        <v>124878842</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1358,7 +1331,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1372,13 +1345,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478839</v>
+        <v>478703</v>
       </c>
       <c r="R8" t="n">
-        <v>6847520</v>
+        <v>6847444</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1434,10 +1407,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124879281</v>
+        <v>124879020</v>
       </c>
       <c r="B9" t="n">
-        <v>56856</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1446,38 +1419,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100065</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478829</v>
+        <v>478692</v>
       </c>
       <c r="R9" t="n">
-        <v>6847313</v>
+        <v>6847427</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1536,7 +1518,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124880942</v>
+        <v>124877779</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1569,20 +1551,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478640</v>
+        <v>478611</v>
       </c>
       <c r="R10" t="n">
-        <v>6847434</v>
+        <v>6847683</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1638,7 +1629,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124878229</v>
+        <v>124879781</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1673,7 +1664,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1683,14 +1674,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478635</v>
+        <v>478839</v>
       </c>
       <c r="R11" t="n">
-        <v>6847637</v>
+        <v>6847520</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1749,7 +1740,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124880417</v>
+        <v>124877547</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1782,20 +1773,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478732</v>
+        <v>478641</v>
       </c>
       <c r="R12" t="n">
-        <v>6847699</v>
+        <v>6847702</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1851,10 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124877547</v>
+        <v>124879281</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>56856</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,50 +1863,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100065</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478641</v>
+        <v>478829</v>
       </c>
       <c r="R13" t="n">
-        <v>6847702</v>
+        <v>6847313</v>
       </c>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2073,7 +2064,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124880228</v>
+        <v>124877917</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2109,14 +2100,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478766</v>
+        <v>478615</v>
       </c>
       <c r="R15" t="n">
-        <v>6847674</v>
+        <v>6847687</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2175,7 +2166,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124878885</v>
+        <v>124880175</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2210,7 +2201,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2224,13 +2215,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478709</v>
+        <v>478795</v>
       </c>
       <c r="R16" t="n">
-        <v>6847442</v>
+        <v>6847652</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2286,7 +2277,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124877633</v>
+        <v>124879880</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2322,14 +2313,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478616</v>
+        <v>478836</v>
       </c>
       <c r="R17" t="n">
-        <v>6847709</v>
+        <v>6847547</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2388,7 +2379,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124877917</v>
+        <v>124880144</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2421,17 +2412,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478615</v>
+        <v>478793</v>
       </c>
       <c r="R18" t="n">
-        <v>6847687</v>
+        <v>6847622</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2490,7 +2490,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124878086</v>
+        <v>124878229</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2523,20 +2523,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478613</v>
+        <v>478635</v>
       </c>
       <c r="R19" t="n">
-        <v>6847629</v>
+        <v>6847637</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2592,7 +2601,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124879945</v>
+        <v>124877633</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2628,14 +2637,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478826</v>
+        <v>478616</v>
       </c>
       <c r="R20" t="n">
-        <v>6847564</v>
+        <v>6847709</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2694,10 +2703,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124878967</v>
+        <v>124880228</v>
       </c>
       <c r="B21" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2706,25 +2715,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2734,13 +2743,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478709</v>
+        <v>478766</v>
       </c>
       <c r="R21" t="n">
-        <v>6847428</v>
+        <v>6847674</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2796,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124880961</v>
+        <v>124878967</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2808,25 +2817,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2836,13 +2845,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478643</v>
+        <v>478709</v>
       </c>
       <c r="R22" t="n">
-        <v>6847426</v>
+        <v>6847428</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2898,7 +2907,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124879020</v>
+        <v>124880417</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -2931,26 +2940,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478692</v>
+        <v>478732</v>
       </c>
       <c r="R23" t="n">
-        <v>6847427</v>
+        <v>6847699</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3009,7 +3009,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124880456</v>
+        <v>124878885</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3042,17 +3042,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478725</v>
+        <v>478709</v>
       </c>
       <c r="R24" t="n">
-        <v>6847685</v>
+        <v>6847442</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3111,7 +3120,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124878415</v>
+        <v>124880539</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3147,17 +3156,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bäverbäcken, Bäverbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478649</v>
+        <v>478707</v>
       </c>
       <c r="R25" t="n">
-        <v>6847660</v>
+        <v>6847701</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3213,7 +3222,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124878260</v>
+        <v>124879945</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3246,29 +3255,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478636</v>
+        <v>478826</v>
       </c>
       <c r="R26" t="n">
-        <v>6847633</v>
+        <v>6847564</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124880144</v>
+        <v>124877845</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3369,17 +3369,17 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478793</v>
+        <v>478609</v>
       </c>
       <c r="R27" t="n">
-        <v>6847622</v>
+        <v>6847684</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>

--- a/artfynd/A 49671-2022 artfynd.xlsx
+++ b/artfynd/A 49671-2022 artfynd.xlsx
@@ -1407,7 +1407,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124879020</v>
+        <v>124877779</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1442,7 +1442,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1452,17 +1452,17 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478692</v>
+        <v>478611</v>
       </c>
       <c r="R9" t="n">
-        <v>6847427</v>
+        <v>6847683</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124877779</v>
+        <v>124879781</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1563,14 +1563,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478611</v>
+        <v>478839</v>
       </c>
       <c r="R10" t="n">
-        <v>6847683</v>
+        <v>6847520</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,7 +1629,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124879781</v>
+        <v>124879020</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1678,13 +1678,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478839</v>
+        <v>478692</v>
       </c>
       <c r="R11" t="n">
-        <v>6847520</v>
+        <v>6847427</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>

--- a/artfynd/A 49671-2022 artfynd.xlsx
+++ b/artfynd/A 49671-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124880961</v>
+        <v>124879781</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -708,17 +708,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478643</v>
+        <v>478839</v>
       </c>
       <c r="R2" t="n">
-        <v>6847426</v>
+        <v>6847520</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124878086</v>
+        <v>124879880</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -813,17 +822,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478613</v>
+        <v>478836</v>
       </c>
       <c r="R3" t="n">
-        <v>6847629</v>
+        <v>6847547</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124880456</v>
+        <v>124879020</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -912,20 +921,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478725</v>
+        <v>478692</v>
       </c>
       <c r="R4" t="n">
-        <v>6847685</v>
+        <v>6847427</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,7 +999,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124880942</v>
+        <v>124880961</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1021,13 +1039,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478640</v>
+        <v>478643</v>
       </c>
       <c r="R5" t="n">
-        <v>6847434</v>
+        <v>6847426</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1083,7 +1101,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124878415</v>
+        <v>124880539</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1119,17 +1137,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bäverbäcken, Bäverbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478649</v>
+        <v>478707</v>
       </c>
       <c r="R6" t="n">
-        <v>6847660</v>
+        <v>6847701</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1185,7 +1203,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124878260</v>
+        <v>124877845</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1220,7 +1238,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1234,13 +1252,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478636</v>
+        <v>478609</v>
       </c>
       <c r="R7" t="n">
-        <v>6847633</v>
+        <v>6847684</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1296,7 +1314,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124878842</v>
+        <v>124880175</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1331,7 +1349,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1345,13 +1363,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478703</v>
+        <v>478795</v>
       </c>
       <c r="R8" t="n">
-        <v>6847444</v>
+        <v>6847652</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1407,7 +1425,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124877779</v>
+        <v>124880228</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1440,26 +1458,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478611</v>
+        <v>478766</v>
       </c>
       <c r="R9" t="n">
-        <v>6847683</v>
+        <v>6847674</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1518,7 +1527,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124879781</v>
+        <v>124878229</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1553,7 +1562,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1563,14 +1572,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478839</v>
+        <v>478635</v>
       </c>
       <c r="R10" t="n">
-        <v>6847520</v>
+        <v>6847637</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1629,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124879020</v>
+        <v>124880456</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1662,29 +1671,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478692</v>
+        <v>478725</v>
       </c>
       <c r="R11" t="n">
-        <v>6847427</v>
+        <v>6847685</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124877547</v>
+        <v>124880882</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1785,17 +1785,17 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478641</v>
+        <v>478627</v>
       </c>
       <c r="R12" t="n">
-        <v>6847702</v>
+        <v>6847481</v>
       </c>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1851,10 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124879281</v>
+        <v>124878842</v>
       </c>
       <c r="B13" t="n">
-        <v>56856</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,38 +1863,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100065</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478829</v>
+        <v>478703</v>
       </c>
       <c r="R13" t="n">
-        <v>6847313</v>
+        <v>6847444</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1953,10 +1962,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124880882</v>
+        <v>124878967</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1965,50 +1974,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478627</v>
+        <v>478709</v>
       </c>
       <c r="R14" t="n">
-        <v>6847481</v>
+        <v>6847428</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124877917</v>
+        <v>124878415</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2104,10 +2104,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478615</v>
+        <v>478649</v>
       </c>
       <c r="R15" t="n">
-        <v>6847687</v>
+        <v>6847660</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2166,7 +2166,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124880175</v>
+        <v>124880144</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2215,13 +2215,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478795</v>
+        <v>478793</v>
       </c>
       <c r="R16" t="n">
-        <v>6847652</v>
+        <v>6847622</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124879880</v>
+        <v>124877633</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2313,14 +2313,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478836</v>
+        <v>478616</v>
       </c>
       <c r="R17" t="n">
-        <v>6847547</v>
+        <v>6847709</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2379,7 +2379,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124880144</v>
+        <v>124878086</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2412,29 +2412,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478793</v>
+        <v>478613</v>
       </c>
       <c r="R18" t="n">
-        <v>6847622</v>
+        <v>6847629</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2490,7 +2481,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124878229</v>
+        <v>124880417</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2523,29 +2514,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478635</v>
+        <v>478732</v>
       </c>
       <c r="R19" t="n">
-        <v>6847637</v>
+        <v>6847699</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2601,7 +2583,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124877633</v>
+        <v>124878885</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2634,17 +2616,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478616</v>
+        <v>478709</v>
       </c>
       <c r="R20" t="n">
-        <v>6847709</v>
+        <v>6847442</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2703,7 +2694,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124880228</v>
+        <v>124877547</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -2736,20 +2727,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478766</v>
+        <v>478641</v>
       </c>
       <c r="R21" t="n">
-        <v>6847674</v>
+        <v>6847702</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2805,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124878967</v>
+        <v>124878260</v>
       </c>
       <c r="B22" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2817,41 +2817,50 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478709</v>
+        <v>478636</v>
       </c>
       <c r="R22" t="n">
-        <v>6847428</v>
+        <v>6847633</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2907,10 +2916,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124880417</v>
+        <v>124879281</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
+        <v>56856</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2919,25 +2928,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100065</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2947,10 +2956,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478732</v>
+        <v>478829</v>
       </c>
       <c r="R23" t="n">
-        <v>6847699</v>
+        <v>6847313</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3009,7 +3018,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124878885</v>
+        <v>124877917</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3042,26 +3051,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478709</v>
+        <v>478615</v>
       </c>
       <c r="R24" t="n">
-        <v>6847442</v>
+        <v>6847687</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3120,7 +3120,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124880539</v>
+        <v>124877779</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3153,20 +3153,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bäverbäcken, Bäverbäcken, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478707</v>
+        <v>478611</v>
       </c>
       <c r="R25" t="n">
-        <v>6847701</v>
+        <v>6847683</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3222,7 +3231,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124879945</v>
+        <v>124880942</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3262,13 +3271,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478826</v>
+        <v>478640</v>
       </c>
       <c r="R26" t="n">
-        <v>6847564</v>
+        <v>6847434</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3324,7 +3333,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124877845</v>
+        <v>124879945</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3357,29 +3366,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478609</v>
+        <v>478826</v>
       </c>
       <c r="R27" t="n">
-        <v>6847684</v>
+        <v>6847564</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>

--- a/artfynd/A 49671-2022 artfynd.xlsx
+++ b/artfynd/A 49671-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124879781</v>
+        <v>124879880</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -708,26 +708,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478839</v>
+        <v>478836</v>
       </c>
       <c r="R2" t="n">
-        <v>6847520</v>
+        <v>6847547</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124879880</v>
+        <v>124878229</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -819,17 +810,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478836</v>
+        <v>478635</v>
       </c>
       <c r="R3" t="n">
-        <v>6847547</v>
+        <v>6847637</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -888,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124879020</v>
+        <v>124878842</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -923,7 +923,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478692</v>
+        <v>478703</v>
       </c>
       <c r="R4" t="n">
-        <v>6847427</v>
+        <v>6847444</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124880961</v>
+        <v>124880228</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1039,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478643</v>
+        <v>478766</v>
       </c>
       <c r="R5" t="n">
-        <v>6847426</v>
+        <v>6847674</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1101,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124880539</v>
+        <v>124880175</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1134,20 +1134,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bäverbäcken, Bäverbäcken, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478707</v>
+        <v>478795</v>
       </c>
       <c r="R6" t="n">
-        <v>6847701</v>
+        <v>6847652</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,7 +1212,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124877845</v>
+        <v>124880417</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1236,29 +1245,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478609</v>
+        <v>478732</v>
       </c>
       <c r="R7" t="n">
-        <v>6847684</v>
+        <v>6847699</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124880175</v>
+        <v>124877845</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1359,17 +1359,17 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478795</v>
+        <v>478609</v>
       </c>
       <c r="R8" t="n">
-        <v>6847652</v>
+        <v>6847684</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124880228</v>
+        <v>124880456</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478766</v>
+        <v>478725</v>
       </c>
       <c r="R9" t="n">
-        <v>6847674</v>
+        <v>6847685</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124878229</v>
+        <v>124880882</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478635</v>
+        <v>478627</v>
       </c>
       <c r="R10" t="n">
-        <v>6847637</v>
+        <v>6847481</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124880456</v>
+        <v>124878885</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1671,17 +1671,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478725</v>
+        <v>478709</v>
       </c>
       <c r="R11" t="n">
-        <v>6847685</v>
+        <v>6847442</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1740,7 +1749,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124880882</v>
+        <v>124880961</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1773,29 +1782,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478627</v>
+        <v>478643</v>
       </c>
       <c r="R12" t="n">
-        <v>6847481</v>
+        <v>6847426</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1851,10 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124878842</v>
+        <v>124879281</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>56856</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,47 +1863,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100065</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478703</v>
+        <v>478829</v>
       </c>
       <c r="R13" t="n">
-        <v>6847444</v>
+        <v>6847313</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1962,10 +1953,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124878967</v>
+        <v>124880144</v>
       </c>
       <c r="B14" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1974,41 +1965,50 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478709</v>
+        <v>478793</v>
       </c>
       <c r="R14" t="n">
-        <v>6847428</v>
+        <v>6847622</v>
       </c>
       <c r="S14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124878415</v>
+        <v>124877547</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2097,20 +2097,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478649</v>
+        <v>478641</v>
       </c>
       <c r="R15" t="n">
-        <v>6847660</v>
+        <v>6847702</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2166,7 +2175,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124880144</v>
+        <v>124879020</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2201,7 +2210,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2215,13 +2224,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478793</v>
+        <v>478692</v>
       </c>
       <c r="R16" t="n">
-        <v>6847622</v>
+        <v>6847427</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2277,7 +2286,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124877633</v>
+        <v>124880942</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2313,17 +2322,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478616</v>
+        <v>478640</v>
       </c>
       <c r="R17" t="n">
-        <v>6847709</v>
+        <v>6847434</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2379,7 +2388,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124878086</v>
+        <v>124878260</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2412,17 +2421,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478613</v>
+        <v>478636</v>
       </c>
       <c r="R18" t="n">
-        <v>6847629</v>
+        <v>6847633</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2481,7 +2499,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124880417</v>
+        <v>124880539</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2517,14 +2535,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Bäverbäcken, Bäverbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478732</v>
+        <v>478707</v>
       </c>
       <c r="R19" t="n">
-        <v>6847699</v>
+        <v>6847701</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2583,7 +2601,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124878885</v>
+        <v>124877633</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2616,26 +2634,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478709</v>
+        <v>478616</v>
       </c>
       <c r="R20" t="n">
-        <v>6847442</v>
+        <v>6847709</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2694,7 +2703,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124877547</v>
+        <v>124878415</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -2727,29 +2736,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478641</v>
+        <v>478649</v>
       </c>
       <c r="R21" t="n">
-        <v>6847702</v>
+        <v>6847660</v>
       </c>
       <c r="S21" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124878260</v>
+        <v>124877917</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -2838,29 +2838,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478636</v>
+        <v>478615</v>
       </c>
       <c r="R22" t="n">
-        <v>6847633</v>
+        <v>6847687</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2916,10 +2907,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124879281</v>
+        <v>124879945</v>
       </c>
       <c r="B23" t="n">
-        <v>56856</v>
+        <v>98101</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2928,25 +2919,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100065</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2956,13 +2947,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478829</v>
+        <v>478826</v>
       </c>
       <c r="R23" t="n">
-        <v>6847313</v>
+        <v>6847564</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3018,7 +3009,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124877917</v>
+        <v>124877779</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3051,17 +3042,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478615</v>
+        <v>478611</v>
       </c>
       <c r="R24" t="n">
-        <v>6847687</v>
+        <v>6847683</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3120,10 +3120,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124877779</v>
+        <v>124878967</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3132,50 +3132,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478611</v>
+        <v>478709</v>
       </c>
       <c r="R25" t="n">
-        <v>6847683</v>
+        <v>6847428</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3231,7 +3222,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124880942</v>
+        <v>124878086</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3267,14 +3258,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478640</v>
+        <v>478613</v>
       </c>
       <c r="R26" t="n">
-        <v>6847434</v>
+        <v>6847629</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3333,7 +3324,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124879945</v>
+        <v>124879781</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3366,17 +3357,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478826</v>
+        <v>478839</v>
       </c>
       <c r="R27" t="n">
-        <v>6847564</v>
+        <v>6847520</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 49671-2022 artfynd.xlsx
+++ b/artfynd/A 49671-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124879880</v>
+        <v>124879281</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>56856</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100065</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478836</v>
+        <v>478829</v>
       </c>
       <c r="R2" t="n">
-        <v>6847547</v>
+        <v>6847313</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124878229</v>
+        <v>124877845</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -812,7 +812,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -826,13 +826,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478635</v>
+        <v>478609</v>
       </c>
       <c r="R3" t="n">
-        <v>6847637</v>
+        <v>6847684</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124878842</v>
+        <v>124879880</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -921,29 +921,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478703</v>
+        <v>478836</v>
       </c>
       <c r="R4" t="n">
-        <v>6847444</v>
+        <v>6847547</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124880228</v>
+        <v>124879020</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1032,20 +1023,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478766</v>
+        <v>478692</v>
       </c>
       <c r="R5" t="n">
-        <v>6847674</v>
+        <v>6847427</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124880417</v>
+        <v>124880961</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1252,13 +1252,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478732</v>
+        <v>478643</v>
       </c>
       <c r="R7" t="n">
-        <v>6847699</v>
+        <v>6847426</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124877845</v>
+        <v>124877547</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1363,13 +1363,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478609</v>
+        <v>478641</v>
       </c>
       <c r="R8" t="n">
-        <v>6847684</v>
+        <v>6847702</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1425,7 +1425,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124880456</v>
+        <v>124880228</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1465,10 +1465,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478725</v>
+        <v>478766</v>
       </c>
       <c r="R9" t="n">
-        <v>6847685</v>
+        <v>6847674</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124880882</v>
+        <v>124880539</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1560,26 +1560,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Bäverbäcken, Bäverbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478627</v>
+        <v>478707</v>
       </c>
       <c r="R10" t="n">
-        <v>6847481</v>
+        <v>6847701</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1638,7 +1629,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124878885</v>
+        <v>124878229</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1673,7 +1664,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1683,14 +1674,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478709</v>
+        <v>478635</v>
       </c>
       <c r="R11" t="n">
-        <v>6847442</v>
+        <v>6847637</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1749,7 +1740,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124880961</v>
+        <v>124879945</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1789,10 +1780,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478643</v>
+        <v>478826</v>
       </c>
       <c r="R12" t="n">
-        <v>6847426</v>
+        <v>6847564</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1851,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124879281</v>
+        <v>124880882</v>
       </c>
       <c r="B13" t="n">
-        <v>56856</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,38 +1854,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100065</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478829</v>
+        <v>478627</v>
       </c>
       <c r="R13" t="n">
-        <v>6847313</v>
+        <v>6847481</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1953,7 +1953,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124880144</v>
+        <v>124878415</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -1986,26 +1986,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478793</v>
+        <v>478649</v>
       </c>
       <c r="R14" t="n">
-        <v>6847622</v>
+        <v>6847660</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2064,7 +2055,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124877547</v>
+        <v>124877633</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2097,29 +2088,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478641</v>
+        <v>478616</v>
       </c>
       <c r="R15" t="n">
-        <v>6847702</v>
+        <v>6847709</v>
       </c>
       <c r="S15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2175,7 +2157,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124879020</v>
+        <v>124879781</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2210,7 +2192,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2224,13 +2206,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478692</v>
+        <v>478839</v>
       </c>
       <c r="R16" t="n">
-        <v>6847427</v>
+        <v>6847520</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2388,10 +2370,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124878260</v>
+        <v>124878967</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2400,50 +2382,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478636</v>
+        <v>478709</v>
       </c>
       <c r="R18" t="n">
-        <v>6847633</v>
+        <v>6847428</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2499,7 +2472,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124880539</v>
+        <v>124878260</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2532,17 +2505,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bäverbäcken, Bäverbäcken, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478707</v>
+        <v>478636</v>
       </c>
       <c r="R19" t="n">
-        <v>6847701</v>
+        <v>6847633</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2601,7 +2583,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124877633</v>
+        <v>124877779</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2634,17 +2616,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478616</v>
+        <v>478611</v>
       </c>
       <c r="R20" t="n">
-        <v>6847709</v>
+        <v>6847683</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2703,7 +2694,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124878415</v>
+        <v>124878842</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -2736,20 +2727,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478649</v>
+        <v>478703</v>
       </c>
       <c r="R21" t="n">
-        <v>6847660</v>
+        <v>6847444</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124877917</v>
+        <v>124880144</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -2838,17 +2838,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478615</v>
+        <v>478793</v>
       </c>
       <c r="R22" t="n">
-        <v>6847687</v>
+        <v>6847622</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2907,7 +2916,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124879945</v>
+        <v>124878086</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -2943,17 +2952,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478826</v>
+        <v>478613</v>
       </c>
       <c r="R23" t="n">
-        <v>6847564</v>
+        <v>6847629</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3009,7 +3018,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124877779</v>
+        <v>124877917</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3042,26 +3051,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478611</v>
+        <v>478615</v>
       </c>
       <c r="R24" t="n">
-        <v>6847683</v>
+        <v>6847687</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3120,10 +3120,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124878967</v>
+        <v>124878885</v>
       </c>
       <c r="B25" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3132,28 +3132,37 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
@@ -3163,10 +3172,10 @@
         <v>478709</v>
       </c>
       <c r="R25" t="n">
-        <v>6847428</v>
+        <v>6847442</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3222,7 +3231,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124878086</v>
+        <v>124880456</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3258,17 +3267,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478613</v>
+        <v>478725</v>
       </c>
       <c r="R26" t="n">
-        <v>6847629</v>
+        <v>6847685</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3324,7 +3333,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124879781</v>
+        <v>124880417</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3357,29 +3366,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478839</v>
+        <v>478732</v>
       </c>
       <c r="R27" t="n">
-        <v>6847520</v>
+        <v>6847699</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>

--- a/artfynd/A 49671-2022 artfynd.xlsx
+++ b/artfynd/A 49671-2022 artfynd.xlsx
@@ -3018,7 +3018,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124877917</v>
+        <v>124878885</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3051,17 +3051,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478615</v>
+        <v>478709</v>
       </c>
       <c r="R24" t="n">
-        <v>6847687</v>
+        <v>6847442</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3120,7 +3129,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124878885</v>
+        <v>124880456</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3153,26 +3162,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478709</v>
+        <v>478725</v>
       </c>
       <c r="R25" t="n">
-        <v>6847442</v>
+        <v>6847685</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3231,7 +3231,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124880456</v>
+        <v>124877917</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3267,14 +3267,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478725</v>
+        <v>478615</v>
       </c>
       <c r="R26" t="n">
-        <v>6847685</v>
+        <v>6847687</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 49671-2022 artfynd.xlsx
+++ b/artfynd/A 49671-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124879281</v>
+        <v>124877845</v>
       </c>
       <c r="B2" t="n">
-        <v>56856</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100065</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478829</v>
+        <v>478609</v>
       </c>
       <c r="R2" t="n">
-        <v>6847313</v>
+        <v>6847684</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124877845</v>
+        <v>124879281</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>56856</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,50 +798,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100065</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478609</v>
+        <v>478829</v>
       </c>
       <c r="R3" t="n">
-        <v>6847684</v>
+        <v>6847313</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>

--- a/artfynd/A 49671-2022 artfynd.xlsx
+++ b/artfynd/A 49671-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124877845</v>
+        <v>124878842</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478609</v>
+        <v>478703</v>
       </c>
       <c r="R2" t="n">
-        <v>6847684</v>
+        <v>6847444</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124879281</v>
+        <v>124878260</v>
       </c>
       <c r="B3" t="n">
-        <v>56856</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,38 +798,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100065</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478829</v>
+        <v>478636</v>
       </c>
       <c r="R3" t="n">
-        <v>6847313</v>
+        <v>6847633</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -888,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124879880</v>
+        <v>124879781</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -921,17 +930,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478836</v>
+        <v>478839</v>
       </c>
       <c r="R4" t="n">
-        <v>6847547</v>
+        <v>6847520</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124879020</v>
+        <v>124878885</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1025,7 +1043,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1039,13 +1057,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478692</v>
+        <v>478709</v>
       </c>
       <c r="R5" t="n">
-        <v>6847427</v>
+        <v>6847442</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124880175</v>
+        <v>124879020</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1136,7 +1154,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1150,13 +1168,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478795</v>
+        <v>478692</v>
       </c>
       <c r="R6" t="n">
-        <v>6847652</v>
+        <v>6847427</v>
       </c>
       <c r="S6" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1212,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124880961</v>
+        <v>124877633</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1248,14 +1266,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478643</v>
+        <v>478616</v>
       </c>
       <c r="R7" t="n">
-        <v>6847426</v>
+        <v>6847709</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1425,7 +1443,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124880228</v>
+        <v>124880882</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1458,20 +1476,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478766</v>
+        <v>478627</v>
       </c>
       <c r="R9" t="n">
-        <v>6847674</v>
+        <v>6847481</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1527,7 +1554,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124880539</v>
+        <v>124880417</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1563,14 +1590,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bäverbäcken, Bäverbäcken, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478707</v>
+        <v>478732</v>
       </c>
       <c r="R10" t="n">
-        <v>6847701</v>
+        <v>6847699</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1629,7 +1656,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124878229</v>
+        <v>124880175</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1664,7 +1691,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1674,17 +1701,17 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478635</v>
+        <v>478795</v>
       </c>
       <c r="R11" t="n">
-        <v>6847637</v>
+        <v>6847652</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1740,7 +1767,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124879945</v>
+        <v>124877845</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1773,20 +1800,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478826</v>
+        <v>478609</v>
       </c>
       <c r="R12" t="n">
-        <v>6847564</v>
+        <v>6847684</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1842,7 +1878,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124880882</v>
+        <v>124877779</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1877,7 +1913,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1887,17 +1923,17 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478627</v>
+        <v>478611</v>
       </c>
       <c r="R13" t="n">
-        <v>6847481</v>
+        <v>6847683</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1953,7 +1989,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124878415</v>
+        <v>124880539</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -1989,17 +2025,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bäverbäcken, Bäverbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478649</v>
+        <v>478707</v>
       </c>
       <c r="R14" t="n">
-        <v>6847660</v>
+        <v>6847701</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2055,7 +2091,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124877633</v>
+        <v>124880228</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2091,14 +2127,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478616</v>
+        <v>478766</v>
       </c>
       <c r="R15" t="n">
-        <v>6847709</v>
+        <v>6847674</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2157,10 +2193,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124879781</v>
+        <v>124878967</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2169,50 +2205,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478839</v>
+        <v>478709</v>
       </c>
       <c r="R16" t="n">
-        <v>6847520</v>
+        <v>6847428</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2268,7 +2295,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124880942</v>
+        <v>124879880</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2308,13 +2335,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478640</v>
+        <v>478836</v>
       </c>
       <c r="R17" t="n">
-        <v>6847434</v>
+        <v>6847547</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2370,10 +2397,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124878967</v>
+        <v>124878086</v>
       </c>
       <c r="B18" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2382,41 +2409,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478709</v>
+        <v>478613</v>
       </c>
       <c r="R18" t="n">
-        <v>6847428</v>
+        <v>6847629</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2472,7 +2499,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124878260</v>
+        <v>124879945</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2505,29 +2532,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478636</v>
+        <v>478826</v>
       </c>
       <c r="R19" t="n">
-        <v>6847633</v>
+        <v>6847564</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2583,7 +2601,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124877779</v>
+        <v>124880144</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2618,7 +2636,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2628,14 +2646,14 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478611</v>
+        <v>478793</v>
       </c>
       <c r="R20" t="n">
-        <v>6847683</v>
+        <v>6847622</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2694,10 +2712,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124878842</v>
+        <v>124879281</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>56856</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2706,47 +2724,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100065</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478703</v>
+        <v>478829</v>
       </c>
       <c r="R21" t="n">
-        <v>6847444</v>
+        <v>6847313</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2805,7 +2814,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124880144</v>
+        <v>124880961</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -2838,26 +2847,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478793</v>
+        <v>478643</v>
       </c>
       <c r="R22" t="n">
-        <v>6847622</v>
+        <v>6847426</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2916,7 +2916,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124878086</v>
+        <v>124880456</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -2952,17 +2952,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478613</v>
+        <v>478725</v>
       </c>
       <c r="R23" t="n">
-        <v>6847629</v>
+        <v>6847685</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124878885</v>
+        <v>124878229</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3063,14 +3063,14 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478709</v>
+        <v>478635</v>
       </c>
       <c r="R24" t="n">
-        <v>6847442</v>
+        <v>6847637</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3129,7 +3129,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124880456</v>
+        <v>124878415</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3165,14 +3165,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478725</v>
+        <v>478649</v>
       </c>
       <c r="R25" t="n">
-        <v>6847685</v>
+        <v>6847660</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3333,7 +3333,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124880417</v>
+        <v>124880942</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3373,10 +3373,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478732</v>
+        <v>478640</v>
       </c>
       <c r="R27" t="n">
-        <v>6847699</v>
+        <v>6847434</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>

--- a/artfynd/A 49671-2022 artfynd.xlsx
+++ b/artfynd/A 49671-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124878842</v>
+        <v>124877845</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478703</v>
+        <v>478609</v>
       </c>
       <c r="R2" t="n">
-        <v>6847444</v>
+        <v>6847684</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124878260</v>
+        <v>124880882</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -831,14 +831,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478636</v>
+        <v>478627</v>
       </c>
       <c r="R3" t="n">
-        <v>6847633</v>
+        <v>6847481</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124879781</v>
+        <v>124880942</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -930,29 +930,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478839</v>
+        <v>478640</v>
       </c>
       <c r="R4" t="n">
-        <v>6847520</v>
+        <v>6847434</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1008,7 +999,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124878885</v>
+        <v>124879781</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1043,7 +1034,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1057,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478709</v>
+        <v>478839</v>
       </c>
       <c r="R5" t="n">
-        <v>6847442</v>
+        <v>6847520</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,7 +1110,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124879020</v>
+        <v>124878229</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1154,7 +1145,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1164,17 +1155,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478692</v>
+        <v>478635</v>
       </c>
       <c r="R6" t="n">
-        <v>6847427</v>
+        <v>6847637</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1230,7 +1221,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124877633</v>
+        <v>124879945</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1266,14 +1257,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478616</v>
+        <v>478826</v>
       </c>
       <c r="R7" t="n">
-        <v>6847709</v>
+        <v>6847564</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,7 +1323,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124877547</v>
+        <v>124880417</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1365,29 +1356,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478641</v>
+        <v>478732</v>
       </c>
       <c r="R8" t="n">
-        <v>6847702</v>
+        <v>6847699</v>
       </c>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1443,7 +1425,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124880882</v>
+        <v>124880228</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1476,29 +1458,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478627</v>
+        <v>478766</v>
       </c>
       <c r="R9" t="n">
-        <v>6847481</v>
+        <v>6847674</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1554,7 +1527,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124880417</v>
+        <v>124880144</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1587,20 +1560,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478732</v>
+        <v>478793</v>
       </c>
       <c r="R10" t="n">
-        <v>6847699</v>
+        <v>6847622</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1656,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124880175</v>
+        <v>124877917</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1689,29 +1671,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478795</v>
+        <v>478615</v>
       </c>
       <c r="R11" t="n">
-        <v>6847652</v>
+        <v>6847687</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1767,7 +1740,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124877845</v>
+        <v>124880539</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1800,29 +1773,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bäverbäcken, Bäverbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478609</v>
+        <v>478707</v>
       </c>
       <c r="R12" t="n">
-        <v>6847684</v>
+        <v>6847701</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1878,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124877779</v>
+        <v>124880961</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1911,26 +1875,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478611</v>
+        <v>478643</v>
       </c>
       <c r="R13" t="n">
-        <v>6847683</v>
+        <v>6847426</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1989,7 +1944,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124880539</v>
+        <v>124879020</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2022,17 +1977,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bäverbäcken, Bäverbäcken, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478707</v>
+        <v>478692</v>
       </c>
       <c r="R14" t="n">
-        <v>6847701</v>
+        <v>6847427</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2091,7 +2055,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124880228</v>
+        <v>124878885</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2124,17 +2088,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478766</v>
+        <v>478709</v>
       </c>
       <c r="R15" t="n">
-        <v>6847674</v>
+        <v>6847442</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2193,10 +2166,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124878967</v>
+        <v>124878415</v>
       </c>
       <c r="B16" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2205,41 +2178,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478709</v>
+        <v>478649</v>
       </c>
       <c r="R16" t="n">
-        <v>6847428</v>
+        <v>6847660</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2295,7 +2268,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124879880</v>
+        <v>124880175</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2328,20 +2301,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478836</v>
+        <v>478795</v>
       </c>
       <c r="R17" t="n">
-        <v>6847547</v>
+        <v>6847652</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2499,7 +2481,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124879945</v>
+        <v>124877633</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2535,14 +2517,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478826</v>
+        <v>478616</v>
       </c>
       <c r="R19" t="n">
-        <v>6847564</v>
+        <v>6847709</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2601,7 +2583,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124880144</v>
+        <v>124878842</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2636,7 +2618,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2650,13 +2632,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478793</v>
+        <v>478703</v>
       </c>
       <c r="R20" t="n">
-        <v>6847622</v>
+        <v>6847444</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2712,10 +2694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124879281</v>
+        <v>124878967</v>
       </c>
       <c r="B21" t="n">
-        <v>56856</v>
+        <v>79891</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2724,25 +2706,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100065</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2752,13 +2734,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478829</v>
+        <v>478709</v>
       </c>
       <c r="R21" t="n">
-        <v>6847313</v>
+        <v>6847428</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2814,7 +2796,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124880961</v>
+        <v>124879880</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -2854,10 +2836,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478643</v>
+        <v>478836</v>
       </c>
       <c r="R22" t="n">
-        <v>6847426</v>
+        <v>6847547</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2916,7 +2898,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124880456</v>
+        <v>124877779</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -2949,17 +2931,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478725</v>
+        <v>478611</v>
       </c>
       <c r="R23" t="n">
-        <v>6847685</v>
+        <v>6847683</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3018,7 +3009,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124878229</v>
+        <v>124880456</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3051,26 +3042,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478635</v>
+        <v>478725</v>
       </c>
       <c r="R24" t="n">
-        <v>6847637</v>
+        <v>6847685</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3129,10 +3111,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124878415</v>
+        <v>124879281</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>56856</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3141,41 +3123,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100065</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478649</v>
+        <v>478829</v>
       </c>
       <c r="R25" t="n">
-        <v>6847660</v>
+        <v>6847313</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3231,7 +3213,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124877917</v>
+        <v>124878260</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3264,20 +3246,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478615</v>
+        <v>478636</v>
       </c>
       <c r="R26" t="n">
-        <v>6847687</v>
+        <v>6847633</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3333,7 +3324,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124880942</v>
+        <v>124877547</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3366,20 +3357,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478640</v>
+        <v>478641</v>
       </c>
       <c r="R27" t="n">
-        <v>6847434</v>
+        <v>6847702</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>

--- a/artfynd/A 49671-2022 artfynd.xlsx
+++ b/artfynd/A 49671-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124877845</v>
+        <v>124879781</v>
       </c>
       <c r="B2" t="n">
         <v>98101</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478609</v>
+        <v>478839</v>
       </c>
       <c r="R2" t="n">
-        <v>6847684</v>
+        <v>6847520</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124880882</v>
+        <v>124880417</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -819,26 +819,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478627</v>
+        <v>478732</v>
       </c>
       <c r="R3" t="n">
-        <v>6847481</v>
+        <v>6847699</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -897,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124880942</v>
+        <v>124878842</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -930,17 +921,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478640</v>
+        <v>478703</v>
       </c>
       <c r="R4" t="n">
-        <v>6847434</v>
+        <v>6847444</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124879781</v>
+        <v>124880942</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1032,29 +1032,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478839</v>
+        <v>478640</v>
       </c>
       <c r="R5" t="n">
-        <v>6847520</v>
+        <v>6847434</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,7 +1101,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124878229</v>
+        <v>124879945</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1143,26 +1134,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478635</v>
+        <v>478826</v>
       </c>
       <c r="R6" t="n">
-        <v>6847637</v>
+        <v>6847564</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,7 +1203,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124879945</v>
+        <v>124877779</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1254,17 +1236,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478826</v>
+        <v>478611</v>
       </c>
       <c r="R7" t="n">
-        <v>6847564</v>
+        <v>6847683</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,7 +1314,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124880417</v>
+        <v>124880456</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1363,13 +1354,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478732</v>
+        <v>478725</v>
       </c>
       <c r="R8" t="n">
-        <v>6847699</v>
+        <v>6847685</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1425,7 +1416,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124880228</v>
+        <v>124880175</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1458,20 +1449,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478766</v>
+        <v>478795</v>
       </c>
       <c r="R9" t="n">
-        <v>6847674</v>
+        <v>6847652</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124880144</v>
+        <v>124878415</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1560,26 +1560,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478793</v>
+        <v>478649</v>
       </c>
       <c r="R10" t="n">
-        <v>6847622</v>
+        <v>6847660</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,10 +1629,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124877917</v>
+        <v>124879281</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>56856</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,41 +1641,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100065</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478615</v>
+        <v>478829</v>
       </c>
       <c r="R11" t="n">
-        <v>6847687</v>
+        <v>6847313</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1740,10 +1731,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124880539</v>
+        <v>124878967</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1752,41 +1743,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bäverbäcken, Bäverbäcken, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478707</v>
+        <v>478709</v>
       </c>
       <c r="R12" t="n">
-        <v>6847701</v>
+        <v>6847428</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1842,7 +1833,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124880961</v>
+        <v>124879020</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1875,20 +1866,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478643</v>
+        <v>478692</v>
       </c>
       <c r="R13" t="n">
-        <v>6847426</v>
+        <v>6847427</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124879020</v>
+        <v>124880961</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -1977,29 +1977,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478692</v>
+        <v>478643</v>
       </c>
       <c r="R14" t="n">
-        <v>6847427</v>
+        <v>6847426</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2055,7 +2046,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124878885</v>
+        <v>124878229</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2090,7 +2081,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2100,14 +2091,14 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478709</v>
+        <v>478635</v>
       </c>
       <c r="R15" t="n">
-        <v>6847442</v>
+        <v>6847637</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2166,7 +2157,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124878415</v>
+        <v>124878885</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2199,17 +2190,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478649</v>
+        <v>478709</v>
       </c>
       <c r="R16" t="n">
-        <v>6847660</v>
+        <v>6847442</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2268,7 +2268,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124880175</v>
+        <v>124880882</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2317,13 +2317,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478795</v>
+        <v>478627</v>
       </c>
       <c r="R17" t="n">
-        <v>6847652</v>
+        <v>6847481</v>
       </c>
       <c r="S17" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124878086</v>
+        <v>124880144</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2412,20 +2412,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478613</v>
+        <v>478793</v>
       </c>
       <c r="R18" t="n">
-        <v>6847629</v>
+        <v>6847622</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2481,7 +2490,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124877633</v>
+        <v>124877917</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2521,10 +2530,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478616</v>
+        <v>478615</v>
       </c>
       <c r="R19" t="n">
-        <v>6847709</v>
+        <v>6847687</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2583,7 +2592,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124878842</v>
+        <v>124877845</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2618,7 +2627,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2628,17 +2637,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478703</v>
+        <v>478609</v>
       </c>
       <c r="R20" t="n">
-        <v>6847444</v>
+        <v>6847684</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2694,10 +2703,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124878967</v>
+        <v>124878086</v>
       </c>
       <c r="B21" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2706,41 +2715,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478709</v>
+        <v>478613</v>
       </c>
       <c r="R21" t="n">
-        <v>6847428</v>
+        <v>6847629</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2796,7 +2805,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124879880</v>
+        <v>124878260</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -2829,20 +2838,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478836</v>
+        <v>478636</v>
       </c>
       <c r="R22" t="n">
-        <v>6847547</v>
+        <v>6847633</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2898,7 +2916,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124877779</v>
+        <v>124880228</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -2931,26 +2949,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478611</v>
+        <v>478766</v>
       </c>
       <c r="R23" t="n">
-        <v>6847683</v>
+        <v>6847674</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3009,7 +3018,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124880456</v>
+        <v>124880539</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3045,17 +3054,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Bäverbäcken, Bäverbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478725</v>
+        <v>478707</v>
       </c>
       <c r="R24" t="n">
-        <v>6847685</v>
+        <v>6847701</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3111,10 +3120,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124879281</v>
+        <v>124877547</v>
       </c>
       <c r="B25" t="n">
-        <v>56856</v>
+        <v>98101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3123,41 +3132,50 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100065</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478829</v>
+        <v>478641</v>
       </c>
       <c r="R25" t="n">
-        <v>6847313</v>
+        <v>6847702</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3213,7 +3231,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124878260</v>
+        <v>124879880</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3246,29 +3264,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478636</v>
+        <v>478836</v>
       </c>
       <c r="R26" t="n">
-        <v>6847633</v>
+        <v>6847547</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3324,7 +3333,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124877547</v>
+        <v>124877633</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3357,29 +3366,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478641</v>
+        <v>478616</v>
       </c>
       <c r="R27" t="n">
-        <v>6847702</v>
+        <v>6847709</v>
       </c>
       <c r="S27" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>

--- a/artfynd/A 49671-2022 artfynd.xlsx
+++ b/artfynd/A 49671-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124879781</v>
+        <v>124879281</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>56856</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100065</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478839</v>
+        <v>478829</v>
       </c>
       <c r="R2" t="n">
-        <v>6847520</v>
+        <v>6847313</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124880417</v>
+        <v>124878229</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -819,20 +810,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478732</v>
+        <v>478635</v>
       </c>
       <c r="R3" t="n">
-        <v>6847699</v>
+        <v>6847637</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124878842</v>
+        <v>124880228</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -921,29 +921,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478703</v>
+        <v>478766</v>
       </c>
       <c r="R4" t="n">
-        <v>6847444</v>
+        <v>6847674</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124880942</v>
+        <v>124880456</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1039,13 +1030,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478640</v>
+        <v>478725</v>
       </c>
       <c r="R5" t="n">
-        <v>6847434</v>
+        <v>6847685</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,7 +1092,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124879945</v>
+        <v>124879020</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1134,20 +1125,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478826</v>
+        <v>478692</v>
       </c>
       <c r="R6" t="n">
-        <v>6847564</v>
+        <v>6847427</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124877779</v>
+        <v>124877633</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1236,26 +1236,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478611</v>
+        <v>478616</v>
       </c>
       <c r="R7" t="n">
-        <v>6847683</v>
+        <v>6847709</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1305,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124880456</v>
+        <v>124878885</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1347,17 +1338,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478725</v>
+        <v>478709</v>
       </c>
       <c r="R8" t="n">
-        <v>6847685</v>
+        <v>6847442</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,7 +1416,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124880175</v>
+        <v>124877779</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478795</v>
+        <v>478611</v>
       </c>
       <c r="R9" t="n">
-        <v>6847652</v>
+        <v>6847683</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124878415</v>
+        <v>124878842</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1560,20 +1560,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478649</v>
+        <v>478703</v>
       </c>
       <c r="R10" t="n">
-        <v>6847660</v>
+        <v>6847444</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1629,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124879281</v>
+        <v>124880539</v>
       </c>
       <c r="B11" t="n">
-        <v>56856</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1641,38 +1650,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100065</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Bäverbäcken, Bäverbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478829</v>
+        <v>478707</v>
       </c>
       <c r="R11" t="n">
-        <v>6847313</v>
+        <v>6847701</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1731,10 +1740,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124878967</v>
+        <v>124880942</v>
       </c>
       <c r="B12" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1743,25 +1752,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1771,13 +1780,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478709</v>
+        <v>478640</v>
       </c>
       <c r="R12" t="n">
-        <v>6847428</v>
+        <v>6847434</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1833,7 +1842,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124879020</v>
+        <v>124878260</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1868,7 +1877,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1878,14 +1887,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478692</v>
+        <v>478636</v>
       </c>
       <c r="R13" t="n">
-        <v>6847427</v>
+        <v>6847633</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1944,7 +1953,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124880961</v>
+        <v>124877547</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -1977,20 +1986,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478643</v>
+        <v>478641</v>
       </c>
       <c r="R14" t="n">
-        <v>6847426</v>
+        <v>6847702</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2046,7 +2064,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124878229</v>
+        <v>124877845</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2081,7 +2099,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2095,13 +2113,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478635</v>
+        <v>478609</v>
       </c>
       <c r="R15" t="n">
-        <v>6847637</v>
+        <v>6847684</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2157,7 +2175,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124878885</v>
+        <v>124879945</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2190,26 +2208,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478709</v>
+        <v>478826</v>
       </c>
       <c r="R16" t="n">
-        <v>6847442</v>
+        <v>6847564</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2268,7 +2277,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124880882</v>
+        <v>124879781</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2303,7 +2312,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2317,13 +2326,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478627</v>
+        <v>478839</v>
       </c>
       <c r="R17" t="n">
-        <v>6847481</v>
+        <v>6847520</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2379,7 +2388,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124880144</v>
+        <v>124880175</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2428,13 +2437,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478793</v>
+        <v>478795</v>
       </c>
       <c r="R18" t="n">
-        <v>6847622</v>
+        <v>6847652</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2490,7 +2499,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124877917</v>
+        <v>124880144</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2523,17 +2532,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478615</v>
+        <v>478793</v>
       </c>
       <c r="R19" t="n">
-        <v>6847687</v>
+        <v>6847622</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2592,7 +2610,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124877845</v>
+        <v>124880882</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2627,7 +2645,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2637,17 +2655,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478609</v>
+        <v>478627</v>
       </c>
       <c r="R20" t="n">
-        <v>6847684</v>
+        <v>6847481</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2703,7 +2721,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124878086</v>
+        <v>124877917</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -2743,13 +2761,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478613</v>
+        <v>478615</v>
       </c>
       <c r="R21" t="n">
-        <v>6847629</v>
+        <v>6847687</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2805,10 +2823,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124878260</v>
+        <v>124878967</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2817,50 +2835,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478636</v>
+        <v>478709</v>
       </c>
       <c r="R22" t="n">
-        <v>6847633</v>
+        <v>6847428</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2916,7 +2925,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124880228</v>
+        <v>124878086</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -2952,17 +2961,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478766</v>
+        <v>478613</v>
       </c>
       <c r="R23" t="n">
-        <v>6847674</v>
+        <v>6847629</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3018,7 +3027,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124880539</v>
+        <v>124878415</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3054,17 +3063,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bäverbäcken, Bäverbäcken, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478707</v>
+        <v>478649</v>
       </c>
       <c r="R24" t="n">
-        <v>6847701</v>
+        <v>6847660</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3120,7 +3129,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124877547</v>
+        <v>124880961</v>
       </c>
       <c r="B25" t="n">
         <v>98101</v>
@@ -3153,29 +3162,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478641</v>
+        <v>478643</v>
       </c>
       <c r="R25" t="n">
-        <v>6847702</v>
+        <v>6847426</v>
       </c>
       <c r="S25" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124877633</v>
+        <v>124880417</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3369,17 +3369,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478616</v>
+        <v>478732</v>
       </c>
       <c r="R27" t="n">
-        <v>6847709</v>
+        <v>6847699</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>

--- a/artfynd/A 49671-2022 artfynd.xlsx
+++ b/artfynd/A 49671-2022 artfynd.xlsx
@@ -2925,7 +2925,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124878086</v>
+        <v>124878415</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -2965,13 +2965,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478613</v>
+        <v>478649</v>
       </c>
       <c r="R23" t="n">
-        <v>6847629</v>
+        <v>6847660</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3027,7 +3027,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124878415</v>
+        <v>124878086</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3067,13 +3067,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478649</v>
+        <v>478613</v>
       </c>
       <c r="R24" t="n">
-        <v>6847660</v>
+        <v>6847629</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>

--- a/artfynd/A 49671-2022 artfynd.xlsx
+++ b/artfynd/A 49671-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124879281</v>
+        <v>124878885</v>
       </c>
       <c r="B2" t="n">
-        <v>56856</v>
+        <v>98101</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100065</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478829</v>
+        <v>478709</v>
       </c>
       <c r="R2" t="n">
-        <v>6847313</v>
+        <v>6847442</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124878229</v>
+        <v>124878842</v>
       </c>
       <c r="B3" t="n">
         <v>98101</v>
@@ -812,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -822,17 +831,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478635</v>
+        <v>478703</v>
       </c>
       <c r="R3" t="n">
-        <v>6847637</v>
+        <v>6847444</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,7 +897,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124880228</v>
+        <v>124880144</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -921,17 +930,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478766</v>
+        <v>478793</v>
       </c>
       <c r="R4" t="n">
-        <v>6847674</v>
+        <v>6847622</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,7 +1008,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124880456</v>
+        <v>124879781</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1023,17 +1041,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478725</v>
+        <v>478839</v>
       </c>
       <c r="R5" t="n">
-        <v>6847685</v>
+        <v>6847520</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,7 +1119,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124879020</v>
+        <v>124877547</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1127,7 +1154,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1137,17 +1164,17 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478692</v>
+        <v>478641</v>
       </c>
       <c r="R6" t="n">
-        <v>6847427</v>
+        <v>6847702</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,7 +1230,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124877633</v>
+        <v>124879945</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1239,14 +1266,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478616</v>
+        <v>478826</v>
       </c>
       <c r="R7" t="n">
-        <v>6847709</v>
+        <v>6847564</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1332,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124878885</v>
+        <v>124880417</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1338,29 +1365,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478709</v>
+        <v>478732</v>
       </c>
       <c r="R8" t="n">
-        <v>6847442</v>
+        <v>6847699</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1416,7 +1434,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124877779</v>
+        <v>124880228</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1449,26 +1467,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478611</v>
+        <v>478766</v>
       </c>
       <c r="R9" t="n">
-        <v>6847683</v>
+        <v>6847674</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1527,7 +1536,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124878842</v>
+        <v>124877845</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1562,7 +1571,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1572,17 +1581,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478703</v>
+        <v>478609</v>
       </c>
       <c r="R10" t="n">
-        <v>6847444</v>
+        <v>6847684</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1638,10 +1647,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124880539</v>
+        <v>124878967</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1650,41 +1659,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bäverbäcken, Bäverbäcken, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478707</v>
+        <v>478709</v>
       </c>
       <c r="R11" t="n">
-        <v>6847701</v>
+        <v>6847428</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1740,7 +1749,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124880942</v>
+        <v>124877633</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1776,17 +1785,17 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478640</v>
+        <v>478616</v>
       </c>
       <c r="R12" t="n">
-        <v>6847434</v>
+        <v>6847709</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1842,7 +1851,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124878260</v>
+        <v>124877779</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1877,7 +1886,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1891,13 +1900,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478636</v>
+        <v>478611</v>
       </c>
       <c r="R13" t="n">
-        <v>6847633</v>
+        <v>6847683</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1953,7 +1962,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124877547</v>
+        <v>124880961</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -1986,29 +1995,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478641</v>
+        <v>478643</v>
       </c>
       <c r="R14" t="n">
-        <v>6847702</v>
+        <v>6847426</v>
       </c>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2064,7 +2064,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124877845</v>
+        <v>124880175</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2109,17 +2109,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478609</v>
+        <v>478795</v>
       </c>
       <c r="R15" t="n">
-        <v>6847684</v>
+        <v>6847652</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124879945</v>
+        <v>124879880</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478826</v>
+        <v>478836</v>
       </c>
       <c r="R16" t="n">
-        <v>6847564</v>
+        <v>6847547</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2277,7 +2277,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124879781</v>
+        <v>124878415</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2310,26 +2310,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478839</v>
+        <v>478649</v>
       </c>
       <c r="R17" t="n">
-        <v>6847520</v>
+        <v>6847660</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2388,7 +2379,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124880175</v>
+        <v>124878086</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2421,29 +2412,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478795</v>
+        <v>478613</v>
       </c>
       <c r="R18" t="n">
-        <v>6847652</v>
+        <v>6847629</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2499,7 +2481,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124880144</v>
+        <v>124880882</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2534,7 +2516,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2548,13 +2530,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478793</v>
+        <v>478627</v>
       </c>
       <c r="R19" t="n">
-        <v>6847622</v>
+        <v>6847481</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2610,7 +2592,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124880882</v>
+        <v>124880539</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -2643,26 +2625,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Bäverbäcken, Bäverbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478627</v>
+        <v>478707</v>
       </c>
       <c r="R20" t="n">
-        <v>6847481</v>
+        <v>6847701</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2721,7 +2694,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124877917</v>
+        <v>124878260</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -2754,20 +2727,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478615</v>
+        <v>478636</v>
       </c>
       <c r="R21" t="n">
-        <v>6847687</v>
+        <v>6847633</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2823,10 +2805,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124878967</v>
+        <v>124880456</v>
       </c>
       <c r="B22" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2835,25 +2817,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2863,13 +2845,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478709</v>
+        <v>478725</v>
       </c>
       <c r="R22" t="n">
-        <v>6847428</v>
+        <v>6847685</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2925,7 +2907,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124878415</v>
+        <v>124880942</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -2961,17 +2943,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478649</v>
+        <v>478640</v>
       </c>
       <c r="R23" t="n">
-        <v>6847660</v>
+        <v>6847434</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3027,7 +3009,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124878086</v>
+        <v>124877917</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3067,13 +3049,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478613</v>
+        <v>478615</v>
       </c>
       <c r="R24" t="n">
-        <v>6847629</v>
+        <v>6847687</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3129,10 +3111,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124880961</v>
+        <v>124879281</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>56856</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3141,25 +3123,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100065</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3169,13 +3151,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478643</v>
+        <v>478829</v>
       </c>
       <c r="R25" t="n">
-        <v>6847426</v>
+        <v>6847313</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3231,7 +3213,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124879880</v>
+        <v>124878229</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3264,17 +3246,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478836</v>
+        <v>478635</v>
       </c>
       <c r="R26" t="n">
-        <v>6847547</v>
+        <v>6847637</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3333,7 +3324,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124880417</v>
+        <v>124879020</v>
       </c>
       <c r="B27" t="n">
         <v>98101</v>
@@ -3366,17 +3357,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478732</v>
+        <v>478692</v>
       </c>
       <c r="R27" t="n">
-        <v>6847699</v>
+        <v>6847427</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>

--- a/artfynd/A 49671-2022 artfynd.xlsx
+++ b/artfynd/A 49671-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124878885</v>
+        <v>124879020</v>
       </c>
       <c r="B2" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478709</v>
+        <v>478692</v>
       </c>
       <c r="R2" t="n">
-        <v>6847442</v>
+        <v>6847427</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124878842</v>
+        <v>124880539</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -819,26 +819,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Bäverbäcken, Bäverbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478703</v>
+        <v>478707</v>
       </c>
       <c r="R3" t="n">
-        <v>6847444</v>
+        <v>6847701</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -897,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124880144</v>
+        <v>124878260</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,7 +923,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -942,17 +933,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478793</v>
+        <v>478636</v>
       </c>
       <c r="R4" t="n">
-        <v>6847622</v>
+        <v>6847633</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1008,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124879781</v>
+        <v>124879880</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,26 +1032,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478839</v>
+        <v>478836</v>
       </c>
       <c r="R5" t="n">
-        <v>6847520</v>
+        <v>6847547</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124877547</v>
+        <v>124880942</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,29 +1134,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478641</v>
+        <v>478640</v>
       </c>
       <c r="R6" t="n">
-        <v>6847702</v>
+        <v>6847434</v>
       </c>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1230,10 +1203,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124879945</v>
+        <v>124877917</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,14 +1239,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478826</v>
+        <v>478615</v>
       </c>
       <c r="R7" t="n">
-        <v>6847564</v>
+        <v>6847687</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1332,10 +1305,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124880417</v>
+        <v>124877845</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1365,20 +1338,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478732</v>
+        <v>478609</v>
       </c>
       <c r="R8" t="n">
-        <v>6847699</v>
+        <v>6847684</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1434,10 +1416,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124880228</v>
+        <v>124877547</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1467,20 +1449,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478766</v>
+        <v>478641</v>
       </c>
       <c r="R9" t="n">
-        <v>6847674</v>
+        <v>6847702</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1536,10 +1527,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124877845</v>
+        <v>124879781</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1571,7 +1562,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1581,17 +1572,17 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478609</v>
+        <v>478839</v>
       </c>
       <c r="R10" t="n">
-        <v>6847684</v>
+        <v>6847520</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1647,10 +1638,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124878967</v>
+        <v>124880175</v>
       </c>
       <c r="B11" t="n">
-        <v>79891</v>
+        <v>98269</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1659,41 +1650,50 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478709</v>
+        <v>478795</v>
       </c>
       <c r="R11" t="n">
-        <v>6847428</v>
+        <v>6847652</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124877633</v>
+        <v>124880961</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1785,14 +1785,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478616</v>
+        <v>478643</v>
       </c>
       <c r="R12" t="n">
-        <v>6847709</v>
+        <v>6847426</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1851,10 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124877779</v>
+        <v>124878967</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>80028</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,50 +1863,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478611</v>
+        <v>478709</v>
       </c>
       <c r="R13" t="n">
-        <v>6847683</v>
+        <v>6847428</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1962,10 +1953,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124880961</v>
+        <v>124880144</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1995,17 +1986,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478643</v>
+        <v>478793</v>
       </c>
       <c r="R14" t="n">
-        <v>6847426</v>
+        <v>6847622</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2064,10 +2064,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124880175</v>
+        <v>124877779</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2109,17 +2109,17 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478795</v>
+        <v>478611</v>
       </c>
       <c r="R15" t="n">
-        <v>6847652</v>
+        <v>6847683</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2175,10 +2175,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124879880</v>
+        <v>124878842</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2208,20 +2208,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478836</v>
+        <v>478703</v>
       </c>
       <c r="R16" t="n">
-        <v>6847547</v>
+        <v>6847444</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2277,10 +2286,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124878415</v>
+        <v>124879945</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2313,14 +2322,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478649</v>
+        <v>478826</v>
       </c>
       <c r="R17" t="n">
-        <v>6847660</v>
+        <v>6847564</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2382,7 +2391,7 @@
         <v>124878086</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2481,10 +2490,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124880882</v>
+        <v>124878885</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2516,7 +2525,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>150</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2530,13 +2539,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>478627</v>
+        <v>478709</v>
       </c>
       <c r="R19" t="n">
-        <v>6847481</v>
+        <v>6847442</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2592,10 +2601,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124880539</v>
+        <v>124877633</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2628,17 +2637,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bäverbäcken, Bäverbäcken, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478707</v>
+        <v>478616</v>
       </c>
       <c r="R20" t="n">
-        <v>6847701</v>
+        <v>6847709</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2694,10 +2703,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124878260</v>
+        <v>124880882</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2729,7 +2738,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2739,14 +2748,14 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478636</v>
+        <v>478627</v>
       </c>
       <c r="R21" t="n">
-        <v>6847633</v>
+        <v>6847481</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2805,10 +2814,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124880456</v>
+        <v>124880417</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2845,13 +2854,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478725</v>
+        <v>478732</v>
       </c>
       <c r="R22" t="n">
-        <v>6847685</v>
+        <v>6847699</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2907,10 +2916,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124880942</v>
+        <v>124879281</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
+        <v>56949</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2919,25 +2928,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100065</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trana</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Grus grus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2947,10 +2956,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>478640</v>
+        <v>478829</v>
       </c>
       <c r="R23" t="n">
-        <v>6847434</v>
+        <v>6847313</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3009,10 +3018,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124877917</v>
+        <v>124880228</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3045,14 +3054,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478615</v>
+        <v>478766</v>
       </c>
       <c r="R24" t="n">
-        <v>6847687</v>
+        <v>6847674</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3111,10 +3120,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124879281</v>
+        <v>124878415</v>
       </c>
       <c r="B25" t="n">
-        <v>56856</v>
+        <v>98269</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3123,41 +3132,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100065</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trana</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Grus grus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478829</v>
+        <v>478649</v>
       </c>
       <c r="R25" t="n">
-        <v>6847313</v>
+        <v>6847660</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3213,10 +3222,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124878229</v>
+        <v>124880456</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3246,26 +3255,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478635</v>
+        <v>478725</v>
       </c>
       <c r="R26" t="n">
-        <v>6847637</v>
+        <v>6847685</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3324,10 +3324,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124879020</v>
+        <v>124878229</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3369,17 +3369,17 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478692</v>
+        <v>478635</v>
       </c>
       <c r="R27" t="n">
-        <v>6847427</v>
+        <v>6847637</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>

--- a/artfynd/A 49671-2022 artfynd.xlsx
+++ b/artfynd/A 49671-2022 artfynd.xlsx
@@ -1527,7 +1527,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124879781</v>
+        <v>124880175</v>
       </c>
       <c r="B10" t="n">
         <v>98269</v>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1576,13 +1576,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478839</v>
+        <v>478795</v>
       </c>
       <c r="R10" t="n">
-        <v>6847520</v>
+        <v>6847652</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1638,7 +1638,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124880175</v>
+        <v>124880961</v>
       </c>
       <c r="B11" t="n">
         <v>98269</v>
@@ -1671,29 +1671,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478795</v>
+        <v>478643</v>
       </c>
       <c r="R11" t="n">
-        <v>6847652</v>
+        <v>6847426</v>
       </c>
       <c r="S11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1749,7 +1740,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124880961</v>
+        <v>124879781</v>
       </c>
       <c r="B12" t="n">
         <v>98269</v>
@@ -1782,17 +1773,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478643</v>
+        <v>478839</v>
       </c>
       <c r="R12" t="n">
-        <v>6847426</v>
+        <v>6847520</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 49671-2022 artfynd.xlsx
+++ b/artfynd/A 49671-2022 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124879020</v>
+        <v>124880942</v>
       </c>
       <c r="B2" t="n">
         <v>98269</v>
@@ -708,26 +708,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478692</v>
+        <v>478640</v>
       </c>
       <c r="R2" t="n">
-        <v>6847427</v>
+        <v>6847434</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -786,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124880539</v>
+        <v>124879781</v>
       </c>
       <c r="B3" t="n">
         <v>98269</v>
@@ -819,20 +810,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bäverbäcken, Bäverbäcken, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478707</v>
+        <v>478839</v>
       </c>
       <c r="R3" t="n">
-        <v>6847701</v>
+        <v>6847520</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124878260</v>
+        <v>124880456</v>
       </c>
       <c r="B4" t="n">
         <v>98269</v>
@@ -921,29 +921,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478636</v>
+        <v>478725</v>
       </c>
       <c r="R4" t="n">
-        <v>6847633</v>
+        <v>6847685</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,7 +990,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124879880</v>
+        <v>124880228</v>
       </c>
       <c r="B5" t="n">
         <v>98269</v>
@@ -1039,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478836</v>
+        <v>478766</v>
       </c>
       <c r="R5" t="n">
-        <v>6847547</v>
+        <v>6847674</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1092,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124880942</v>
+        <v>124880961</v>
       </c>
       <c r="B6" t="n">
         <v>98269</v>
@@ -1141,13 +1132,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478640</v>
+        <v>478643</v>
       </c>
       <c r="R6" t="n">
-        <v>6847434</v>
+        <v>6847426</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,7 +1194,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124877917</v>
+        <v>124880175</v>
       </c>
       <c r="B7" t="n">
         <v>98269</v>
@@ -1236,20 +1227,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478615</v>
+        <v>478795</v>
       </c>
       <c r="R7" t="n">
-        <v>6847687</v>
+        <v>6847652</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124877845</v>
+        <v>124878260</v>
       </c>
       <c r="B8" t="n">
         <v>98269</v>
@@ -1340,7 +1340,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1354,13 +1354,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478609</v>
+        <v>478636</v>
       </c>
       <c r="R8" t="n">
-        <v>6847684</v>
+        <v>6847633</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1416,7 +1416,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124877547</v>
+        <v>124878086</v>
       </c>
       <c r="B9" t="n">
         <v>98269</v>
@@ -1449,29 +1449,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478641</v>
+        <v>478613</v>
       </c>
       <c r="R9" t="n">
-        <v>6847702</v>
+        <v>6847629</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1527,7 +1518,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124880175</v>
+        <v>124878842</v>
       </c>
       <c r="B10" t="n">
         <v>98269</v>
@@ -1562,7 +1553,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1576,13 +1567,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478795</v>
+        <v>478703</v>
       </c>
       <c r="R10" t="n">
-        <v>6847652</v>
+        <v>6847444</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1638,7 +1629,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124880961</v>
+        <v>124879020</v>
       </c>
       <c r="B11" t="n">
         <v>98269</v>
@@ -1671,20 +1662,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478643</v>
+        <v>478692</v>
       </c>
       <c r="R11" t="n">
-        <v>6847426</v>
+        <v>6847427</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124879781</v>
+        <v>124878415</v>
       </c>
       <c r="B12" t="n">
         <v>98269</v>
@@ -1773,26 +1773,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478839</v>
+        <v>478649</v>
       </c>
       <c r="R12" t="n">
-        <v>6847520</v>
+        <v>6847660</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1851,10 +1842,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124878967</v>
+        <v>124877845</v>
       </c>
       <c r="B13" t="n">
-        <v>80028</v>
+        <v>98269</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1863,38 +1854,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>478709</v>
+        <v>478609</v>
       </c>
       <c r="R13" t="n">
-        <v>6847428</v>
+        <v>6847684</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1953,7 +1953,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124880144</v>
+        <v>124880417</v>
       </c>
       <c r="B14" t="n">
         <v>98269</v>
@@ -1986,29 +1986,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>478793</v>
+        <v>478732</v>
       </c>
       <c r="R14" t="n">
-        <v>6847622</v>
+        <v>6847699</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2064,7 +2055,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124877779</v>
+        <v>124879880</v>
       </c>
       <c r="B15" t="n">
         <v>98269</v>
@@ -2097,26 +2088,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>478611</v>
+        <v>478836</v>
       </c>
       <c r="R15" t="n">
-        <v>6847683</v>
+        <v>6847547</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2175,7 +2157,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124878842</v>
+        <v>124878229</v>
       </c>
       <c r="B16" t="n">
         <v>98269</v>
@@ -2210,7 +2192,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2220,17 +2202,17 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>478703</v>
+        <v>478635</v>
       </c>
       <c r="R16" t="n">
-        <v>6847444</v>
+        <v>6847637</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2286,7 +2268,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124879945</v>
+        <v>124880144</v>
       </c>
       <c r="B17" t="n">
         <v>98269</v>
@@ -2319,17 +2301,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>478826</v>
+        <v>478793</v>
       </c>
       <c r="R17" t="n">
-        <v>6847564</v>
+        <v>6847622</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2388,7 +2379,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124878086</v>
+        <v>124877633</v>
       </c>
       <c r="B18" t="n">
         <v>98269</v>
@@ -2428,13 +2419,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>478613</v>
+        <v>478616</v>
       </c>
       <c r="R18" t="n">
-        <v>6847629</v>
+        <v>6847709</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2601,7 +2592,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124877633</v>
+        <v>124879945</v>
       </c>
       <c r="B20" t="n">
         <v>98269</v>
@@ -2637,14 +2628,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
+          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>478616</v>
+        <v>478826</v>
       </c>
       <c r="R20" t="n">
-        <v>6847709</v>
+        <v>6847564</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2703,10 +2694,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124880882</v>
+        <v>124878967</v>
       </c>
       <c r="B21" t="n">
-        <v>98269</v>
+        <v>80028</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2715,50 +2706,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>478627</v>
+        <v>478709</v>
       </c>
       <c r="R21" t="n">
-        <v>6847481</v>
+        <v>6847428</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2814,7 +2796,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124880417</v>
+        <v>124880882</v>
       </c>
       <c r="B22" t="n">
         <v>98269</v>
@@ -2847,17 +2829,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bävertjärnen, Bävertjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>478732</v>
+        <v>478627</v>
       </c>
       <c r="R22" t="n">
-        <v>6847699</v>
+        <v>6847481</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -3018,7 +3009,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124880228</v>
+        <v>124877547</v>
       </c>
       <c r="B24" t="n">
         <v>98269</v>
@@ -3051,20 +3042,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>478766</v>
+        <v>478641</v>
       </c>
       <c r="R24" t="n">
-        <v>6847674</v>
+        <v>6847702</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3120,7 +3120,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124878415</v>
+        <v>124877779</v>
       </c>
       <c r="B25" t="n">
         <v>98269</v>
@@ -3153,17 +3153,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>478649</v>
+        <v>478611</v>
       </c>
       <c r="R25" t="n">
-        <v>6847660</v>
+        <v>6847683</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3222,7 +3231,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124880456</v>
+        <v>124880539</v>
       </c>
       <c r="B26" t="n">
         <v>98269</v>
@@ -3258,17 +3267,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bävertjärnen, Bävertjärnen, Dlr</t>
+          <t>Bäverbäcken, Bäverbäcken, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>478725</v>
+        <v>478707</v>
       </c>
       <c r="R26" t="n">
-        <v>6847685</v>
+        <v>6847701</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3324,7 +3333,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124878229</v>
+        <v>124877917</v>
       </c>
       <c r="B27" t="n">
         <v>98269</v>
@@ -3357,26 +3366,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Örnsjökojan, Örnsjökojan, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>478635</v>
+        <v>478615</v>
       </c>
       <c r="R27" t="n">
-        <v>6847637</v>
+        <v>6847687</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
